--- a/samples/sample.xlsx
+++ b/samples/sample.xlsx
@@ -10,6 +10,7 @@
     <x:sheet name="root" sheetId="2" r:id="rId3"/>
     <x:sheet name="profile" sheetId="3" r:id="rId4"/>
     <x:sheet name="items" sheetId="4" r:id="rId5"/>
+    <x:sheet name="nickNames" sheetId="5" r:id="rId14"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -47,6 +48,20 @@
             <x:family val="2"/>
           </x:rPr>
           <x:t>array:items</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:rPr>
+            <x:vertAlign val="baseline"/>
+            <x:sz val="9"/>
+            <x:color rgb="FF000000"/>
+            <x:rFont val="Tahoma"/>
+            <x:family val="2"/>
+          </x:rPr>
+          <x:t>scalar-array:nickNames</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -134,7 +149,7 @@
     <x:t>object</x:t>
   </x:si>
   <x:si>
-    <x:t>rootを単一objectまたはarrayとして出力します。</x:t>
+    <x:t>nickNames</x:t>
   </x:si>
   <x:si>
     <x:t>emptyCell</x:t>
@@ -195,6 +210,18 @@
   </x:si>
   <x:si>
     <x:t>Orange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rootを単一object、object配列、またはスカラー配列として出力します。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Allie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ali</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -625,7 +652,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" ht="14.25" customHeight="1">
@@ -674,11 +701,11 @@
   <x:dimension ref="A1:G4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="4" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="7" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="5" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="8" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7" ht="23" customHeight="1">
+    <x:row r="1" spans="1:8" ht="23" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -691,8 +718,11 @@
       <x:c r="D1" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7">
+      <x:c r="E1" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8">
       <x:c r="A2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -704,6 +734,9 @@
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>20</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -813,4 +846,48 @@
   <x:legacyDrawing r:id="rId13"/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B3"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="2" width="12.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:2" ht="23" customHeight="1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2" ht="15" customHeight="1">
+      <x:c r="A2" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:2" ht="15" customHeight="1">
+      <x:c r="A3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>